--- a/data/mini-example-resilience/Power_Parameters.xlsx
+++ b/data/mini-example-resilience/Power_Parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B67904-1858-48BD-B9AB-28337245DCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E0C823-AAA5-4E21-A801-A94794A4B753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1577,7 +1577,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="10">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>17</v>
@@ -1606,7 +1606,7 @@
         <v>66</v>
       </c>
       <c r="C63" s="10">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>37</v>
